--- a/Figures/Heatmaps/IG-heatmap.xlsx
+++ b/Figures/Heatmaps/IG-heatmap.xlsx
@@ -223,16 +223,10 @@
     <t xml:space="preserve">Tropical stack</t>
   </si>
   <si>
-    <t xml:space="preserve">Herbert et al. (2010)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ΔMOT (°C)</t>
-  </si>
-  <si>
-    <t>ΔMOT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Clark et al. (2025)</t>
+    <t xml:space="preserve">SST (°C)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Herbert et al. (2017)</t>
   </si>
   <si>
     <t xml:space="preserve">Terrestrial archives</t>
@@ -275,6 +269,12 @@
   </si>
   <si>
     <t xml:space="preserve">Zhao et al. (2021)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Heqing Basin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wang et al. (2025)</t>
   </si>
   <si>
     <t xml:space="preserve">AP (%) (excl. Gramineae and aquatic/semi-aquatic taxa)</t>
@@ -357,7 +357,7 @@
       <color rgb="FFF1F1F1"/>
     </font>
   </fonts>
-  <fills count="230">
+  <fills count="232">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1232,47 +1232,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD65959"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD45151"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDF7F7F"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDE7878"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3D0D0"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC7070"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD55353"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC30E0E"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEBAFAF"/>
+        <fgColor rgb="FFFBEFEF"/>
       </patternFill>
     </fill>
     <fill>
@@ -1282,12 +1242,27 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFEBADAD"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC41111"/>
+        <fgColor rgb="FFEEB9B9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE08181"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8E2E2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF6DADA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCB2E2E"/>
       </patternFill>
     </fill>
     <fill>
@@ -1303,6 +1278,11 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFC41111"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFC71E1E"/>
       </patternFill>
     </fill>
@@ -1338,7 +1318,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFCB2E2E"/>
+        <fgColor rgb="FFDC7070"/>
       </patternFill>
     </fill>
     <fill>
@@ -1348,6 +1328,11 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFEBAFAF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFE38F8F"/>
       </patternFill>
     </fill>
@@ -1363,7 +1348,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE08181"/>
+        <fgColor rgb="FFC30E0E"/>
       </patternFill>
     </fill>
     <fill>
@@ -1378,6 +1363,11 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFD45151"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFEEBABA"/>
       </patternFill>
     </fill>
@@ -1388,12 +1378,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC40F0F"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF7DFDF"/>
+        <fgColor rgb="FFDF7F7F"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1C8C8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD86363"/>
       </patternFill>
     </fill>
     <fill>
@@ -1403,22 +1398,22 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFD55454"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFAEAEA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3D0D0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFDC7171"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1C8C8"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC61818"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD55454"/>
       </patternFill>
     </fill>
     <fill>
@@ -1429,12 +1424,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFBEFEF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEEB9B9"/>
+        <fgColor rgb="FFDA6A6A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9E7E7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC61818"/>
       </patternFill>
     </fill>
     <fill>
@@ -1469,6 +1469,11 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFD65959"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFCF4F4"/>
       </patternFill>
     </fill>
@@ -1489,6 +1494,11 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFD55353"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFCA2A2A"/>
       </patternFill>
     </fill>
@@ -1508,7 +1518,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="16">
+  <borders count="15">
     <border>
       <left style="none"/>
       <right style="none"/>
@@ -1636,19 +1646,6 @@
       <diagonal style="none"/>
     </border>
     <border>
-      <left style="none"/>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal style="none"/>
-    </border>
-    <border>
       <left style="thin">
         <color auto="1"/>
       </left>
@@ -1689,7 +1686,7 @@
   <cellStyleXfs count="1">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellStyleXfs>
-  <cellXfs count="392">
+  <cellXfs count="373">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" quotePrefix="0" pivotButton="0"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1" quotePrefix="0" pivotButton="0">
       <alignment horizontal="left"/>
@@ -2400,69 +2397,6 @@
     <xf fontId="4" fillId="4" borderId="6" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf fontId="4" fillId="175" borderId="8" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf fontId="4" fillId="10" borderId="8" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf fontId="4" fillId="176" borderId="8" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf fontId="4" fillId="152" borderId="8" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf fontId="3" fillId="150" borderId="8" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf fontId="4" fillId="31" borderId="8" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf fontId="4" fillId="177" borderId="8" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf fontId="3" fillId="161" borderId="8" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf fontId="4" fillId="178" borderId="8" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf fontId="4" fillId="155" borderId="8" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf fontId="3" fillId="30" borderId="8" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf fontId="3" fillId="140" borderId="8" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf fontId="4" fillId="131" borderId="8" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf fontId="3" fillId="179" borderId="8" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf fontId="4" fillId="180" borderId="8" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf fontId="4" fillId="100" borderId="8" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf fontId="3" fillId="80" borderId="8" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf fontId="4" fillId="154" borderId="8" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf fontId="3" fillId="42" borderId="8" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf fontId="4" fillId="181" borderId="8" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf fontId="4" fillId="172" borderId="9" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
-      <alignment horizontal="center"/>
-    </xf>
     <xf fontId="2" fillId="0" borderId="10" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2472,84 +2406,69 @@
     <xf fontId="3" fillId="0" borderId="11" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf fontId="4" fillId="43" borderId="11" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf fontId="4" fillId="182" borderId="11" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf fontId="3" fillId="5" borderId="11" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf fontId="3" fillId="183" borderId="11" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf fontId="4" fillId="25" borderId="11" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf fontId="3" fillId="184" borderId="11" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf fontId="3" fillId="74" borderId="11" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf fontId="3" fillId="150" borderId="11" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf fontId="3" fillId="16" borderId="11" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf fontId="3" fillId="126" borderId="11" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf fontId="3" fillId="185" borderId="11" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf fontId="3" fillId="71" borderId="11" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf fontId="3" fillId="15" borderId="11" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf fontId="4" fillId="167" borderId="11" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf fontId="4" fillId="67" borderId="11" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf fontId="4" fillId="10" borderId="11" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf fontId="4" fillId="154" borderId="11" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf fontId="4" fillId="102" borderId="11" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf fontId="4" fillId="157" borderId="11" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf fontId="4" fillId="17" borderId="11" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf fontId="4" fillId="4" borderId="11" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf fontId="4" fillId="147" borderId="11" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf fontId="4" fillId="186" borderId="12" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf fontId="1" fillId="187" borderId="13" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+    <xf fontId="3" fillId="69" borderId="3" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="92" borderId="3" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="3" fillId="175" borderId="3" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="3" fillId="88" borderId="3" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="3" fillId="148" borderId="3" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="171" borderId="3" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="3" fillId="176" borderId="3" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="3" fillId="79" borderId="3" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="3" fillId="177" borderId="3" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="3" fillId="51" borderId="3" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="3" fillId="150" borderId="3" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="178" borderId="3" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="3" fillId="179" borderId="3" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="3" fillId="180" borderId="3" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="37" borderId="3" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="3" fillId="38" borderId="3" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="124" borderId="3" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="47" borderId="3" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="181" borderId="3" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="1" fillId="182" borderId="12" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
       <alignment horizontal="center" textRotation="90" vertical="center"/>
     </xf>
     <xf fontId="4" fillId="100" borderId="3" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf fontId="4" fillId="47" borderId="3" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
-      <alignment horizontal="center"/>
-    </xf>
     <xf fontId="4" fillId="162" borderId="3" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
       <alignment horizontal="center"/>
     </xf>
@@ -2562,13 +2481,34 @@
     <xf fontId="4" fillId="154" borderId="3" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
       <alignment horizontal="center"/>
     </xf>
+    <xf fontId="4" fillId="183" borderId="3" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="184" borderId="3" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="98" borderId="3" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="185" borderId="3" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="186" borderId="3" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="187" borderId="3" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="149" borderId="3" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
     <xf fontId="4" fillId="188" borderId="3" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf fontId="4" fillId="186" borderId="3" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf fontId="4" fillId="98" borderId="3" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+    <xf fontId="4" fillId="164" borderId="3" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="155" borderId="3" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
       <alignment horizontal="center"/>
     </xf>
     <xf fontId="4" fillId="189" borderId="3" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
@@ -2580,82 +2520,76 @@
     <xf fontId="4" fillId="191" borderId="3" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf fontId="4" fillId="149" borderId="3" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf fontId="4" fillId="192" borderId="3" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf fontId="4" fillId="164" borderId="3" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf fontId="4" fillId="155" borderId="3" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf fontId="4" fillId="193" borderId="3" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf fontId="4" fillId="194" borderId="3" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf fontId="4" fillId="195" borderId="3" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
-      <alignment horizontal="center"/>
-    </xf>
     <xf fontId="4" fillId="29" borderId="3" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
       <alignment horizontal="center"/>
     </xf>
     <xf fontId="4" fillId="4" borderId="4" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf fontId="0" fillId="187" borderId="14" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+    <xf fontId="0" fillId="182" borderId="13" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
       <alignment horizontal="center" textRotation="90" vertical="center"/>
     </xf>
-    <xf fontId="4" fillId="180" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf fontId="4" fillId="196" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+    <xf fontId="4" fillId="192" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="181" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="193" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="3" fillId="194" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="98" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="102" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="192" borderId="6" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="195" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="135" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="110" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="3" fillId="196" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
       <alignment horizontal="center"/>
     </xf>
     <xf fontId="4" fillId="197" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf fontId="3" fillId="183" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf fontId="4" fillId="98" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf fontId="4" fillId="102" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf fontId="4" fillId="180" borderId="6" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
-      <alignment horizontal="center"/>
-    </xf>
     <xf fontId="4" fillId="198" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf fontId="4" fillId="135" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf fontId="4" fillId="110" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+    <xf fontId="3" fillId="15" borderId="6" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="6" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="3" fillId="109" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="178" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
       <alignment horizontal="center"/>
     </xf>
     <xf fontId="3" fillId="199" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf fontId="4" fillId="200" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf fontId="4" fillId="182" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf fontId="3" fillId="15" borderId="6" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf fontId="4" fillId="6" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf fontId="3" fillId="109" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+    <xf fontId="3" fillId="200" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="3" fillId="130" borderId="6" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="189" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
       <alignment horizontal="center"/>
     </xf>
     <xf fontId="4" fillId="201" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
@@ -2667,91 +2601,91 @@
     <xf fontId="3" fillId="203" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf fontId="3" fillId="130" borderId="6" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf fontId="4" fillId="193" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf fontId="4" fillId="176" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf fontId="3" fillId="204" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+    <xf fontId="4" fillId="204" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="201" borderId="6" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="87" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="111" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
       <alignment horizontal="center"/>
     </xf>
     <xf fontId="3" fillId="205" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf fontId="4" fillId="177" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf fontId="4" fillId="176" borderId="6" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
-      <alignment horizontal="center"/>
-    </xf>
     <xf fontId="4" fillId="206" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
       <alignment horizontal="center"/>
     </xf>
     <xf fontId="3" fillId="207" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf fontId="4" fillId="73" borderId="6" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf fontId="3" fillId="208" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf fontId="3" fillId="179" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+    <xf fontId="4" fillId="208" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="3" fillId="209" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="101" borderId="6" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="3" fillId="210" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
       <alignment horizontal="center"/>
     </xf>
     <xf fontId="4" fillId="86" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf fontId="4" fillId="209" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf fontId="3" fillId="210" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+    <xf fontId="4" fillId="211" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
       <alignment horizontal="center"/>
     </xf>
     <xf fontId="3" fillId="107" borderId="6" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf fontId="4" fillId="195" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf fontId="4" fillId="192" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf fontId="4" fillId="87" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf fontId="4" fillId="186" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf fontId="4" fillId="211" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
-      <alignment horizontal="center"/>
-    </xf>
     <xf fontId="4" fillId="212" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf fontId="4" fillId="213" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="3" fillId="214" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="63" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="3" fillId="95" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
       <alignment horizontal="center"/>
     </xf>
     <xf fontId="4" fillId="191" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
       <alignment horizontal="center"/>
     </xf>
+    <xf fontId="4" fillId="188" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="184" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="215" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="187" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
     <xf fontId="4" fillId="17" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf fontId="4" fillId="213" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf fontId="4" fillId="194" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+    <xf fontId="4" fillId="190" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
       <alignment horizontal="center"/>
     </xf>
     <xf fontId="4" fillId="25" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf fontId="3" fillId="214" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf fontId="3" fillId="215" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+    <xf fontId="3" fillId="175" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="3" fillId="177" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
       <alignment horizontal="center"/>
     </xf>
     <xf fontId="4" fillId="216" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
@@ -2772,7 +2706,7 @@
     <xf fontId="4" fillId="220" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf fontId="4" fillId="209" borderId="6" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+    <xf fontId="4" fillId="211" borderId="6" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
       <alignment horizontal="center"/>
     </xf>
     <xf fontId="4" fillId="101" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
@@ -2781,43 +2715,43 @@
     <xf fontId="3" fillId="221" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf fontId="4" fillId="175" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf fontId="3" fillId="222" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+    <xf fontId="4" fillId="222" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="3" fillId="223" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
       <alignment horizontal="center"/>
     </xf>
     <xf fontId="3" fillId="9" borderId="6" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf fontId="3" fillId="223" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
-      <alignment horizontal="center"/>
-    </xf>
     <xf fontId="3" fillId="224" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
       <alignment horizontal="center"/>
     </xf>
     <xf fontId="3" fillId="225" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
       <alignment horizontal="center"/>
     </xf>
+    <xf fontId="3" fillId="226" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
     <xf fontId="4" fillId="131" borderId="6" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf fontId="4" fillId="181" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf fontId="4" fillId="226" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
-      <alignment horizontal="center"/>
-    </xf>
     <xf fontId="4" fillId="227" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
       <alignment horizontal="center"/>
     </xf>
     <xf fontId="4" fillId="228" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf fontId="0" fillId="187" borderId="15" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+    <xf fontId="4" fillId="229" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="230" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="0" fillId="182" borderId="14" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
       <alignment horizontal="center" textRotation="90" vertical="center"/>
     </xf>
-    <xf fontId="4" fillId="201" borderId="8" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+    <xf fontId="4" fillId="178" borderId="8" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
       <alignment horizontal="center"/>
     </xf>
     <xf fontId="4" fillId="62" borderId="8" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
@@ -2841,7 +2775,7 @@
     <xf fontId="4" fillId="101" borderId="8" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf fontId="4" fillId="229" borderId="8" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+    <xf fontId="4" fillId="231" borderId="8" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
       <alignment horizontal="center"/>
     </xf>
     <xf fontId="4" fillId="157" borderId="8" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
@@ -2850,13 +2784,19 @@
     <xf fontId="4" fillId="65" borderId="8" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
       <alignment horizontal="center"/>
     </xf>
+    <xf fontId="3" fillId="161" borderId="8" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="222" borderId="8" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
     <xf fontId="3" fillId="221" borderId="8" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
       <alignment horizontal="center"/>
     </xf>
     <xf fontId="4" fillId="103" borderId="8" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf fontId="3" fillId="183" borderId="8" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+    <xf fontId="3" fillId="194" borderId="8" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
       <alignment horizontal="center"/>
     </xf>
     <xf fontId="4" fillId="145" borderId="8" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
@@ -4595,700 +4535,700 @@
     </row>
     <row r="15">
       <c r="A15" s="32"/>
-      <c r="B15" s="102"/>
-      <c r="C15" s="103" t="s">
+      <c r="B15" s="237" t="s">
+        <v>50</v>
+      </c>
+      <c r="C15" s="238" t="s">
         <v>49</v>
       </c>
-      <c r="D15" s="104" t="s">
-        <v>50</v>
-      </c>
-      <c r="E15" s="237">
-        <v>1.474</v>
-      </c>
-      <c r="F15" s="120">
-        <v>2.036</v>
-      </c>
-      <c r="G15" s="238">
-        <v>1.2809999999999999</v>
-      </c>
-      <c r="H15" s="237">
-        <v>1.472</v>
-      </c>
-      <c r="I15" s="239">
-        <v>1.5229999999999999</v>
-      </c>
-      <c r="J15" s="240">
-        <v>1.696</v>
-      </c>
-      <c r="K15" s="241">
-        <v>1.038</v>
-      </c>
-      <c r="L15" s="242">
-        <v>1.1699999999999999</v>
-      </c>
-      <c r="M15" s="115">
-        <v>1.145</v>
-      </c>
-      <c r="N15" s="243">
-        <v>1.2310000000000001</v>
-      </c>
-      <c r="O15" s="244">
-        <v>1.0309999999999999</v>
-      </c>
-      <c r="P15" s="245">
-        <v>1.274</v>
-      </c>
-      <c r="Q15" s="246">
-        <v>1.375</v>
-      </c>
-      <c r="R15" s="247">
-        <v>0.58899999999999997</v>
-      </c>
-      <c r="S15" s="248">
-        <v>0.73199999999999998</v>
-      </c>
-      <c r="T15" s="249">
-        <v>1.181</v>
-      </c>
-      <c r="U15" s="250">
-        <v>0.71799999999999997</v>
-      </c>
-      <c r="V15" s="251">
-        <v>1.3280000000000001</v>
-      </c>
-      <c r="W15" s="252">
-        <v>1.466</v>
-      </c>
-      <c r="X15" s="121">
-        <v>0.42099999999999999</v>
-      </c>
-      <c r="Y15" s="253">
-        <v>1.0780000000000001</v>
-      </c>
-      <c r="Z15" s="254">
-        <v>1.855</v>
-      </c>
-      <c r="AA15" s="255">
-        <v>0.98599999999999999</v>
-      </c>
-      <c r="AB15" s="256">
-        <v>1.51</v>
-      </c>
-      <c r="AC15" s="257">
-        <v>1.4830000000000001</v>
+      <c r="D15" s="239" t="s">
+        <v>51</v>
+      </c>
+      <c r="E15" s="240">
+        <v>27.009</v>
+      </c>
+      <c r="F15" s="241">
+        <v>27.661000000000001</v>
+      </c>
+      <c r="G15" s="242">
+        <v>26.954999999999998</v>
+      </c>
+      <c r="H15" s="243">
+        <v>27.181999999999999</v>
+      </c>
+      <c r="I15" s="244">
+        <v>27.300000000000001</v>
+      </c>
+      <c r="J15" s="245">
+        <v>27.532</v>
+      </c>
+      <c r="K15" s="246">
+        <v>26.937000000000001</v>
+      </c>
+      <c r="L15" s="247">
+        <v>27.132000000000001</v>
+      </c>
+      <c r="M15" s="247">
+        <v>27.134</v>
+      </c>
+      <c r="N15" s="248">
+        <v>27.280999999999999</v>
+      </c>
+      <c r="O15" s="249">
+        <v>27.146000000000001</v>
+      </c>
+      <c r="P15" s="250">
+        <v>27.446999999999999</v>
+      </c>
+      <c r="Q15" s="251">
+        <v>27.617999999999999</v>
+      </c>
+      <c r="R15" s="21">
+        <v>26.852</v>
+      </c>
+      <c r="S15" s="252">
+        <v>27.033999999999999</v>
+      </c>
+      <c r="T15" s="144">
+        <v>27.516999999999999</v>
+      </c>
+      <c r="U15" s="253">
+        <v>27.079999999999998</v>
+      </c>
+      <c r="V15" s="132">
+        <v>27.734999999999999</v>
+      </c>
+      <c r="W15" s="254">
+        <v>27.920999999999999</v>
+      </c>
+      <c r="X15" s="255">
+        <v>26.907</v>
+      </c>
+      <c r="Y15" s="256">
+        <v>27.596</v>
+      </c>
+      <c r="Z15" s="10">
+        <v>28.407</v>
+      </c>
+      <c r="AA15" s="257">
+        <v>27.565000000000001</v>
+      </c>
+      <c r="AB15" s="258">
+        <v>28.122</v>
+      </c>
+      <c r="AC15" s="258">
+        <v>28.125</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="32"/>
-      <c r="B16" s="258" t="s">
-        <v>51</v>
-      </c>
-      <c r="C16" s="259" t="s">
+      <c r="A16" s="259" t="s">
         <v>52</v>
       </c>
-      <c r="D16" s="260" t="s">
+      <c r="B16" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="E16" s="261">
-        <v>0</v>
-      </c>
-      <c r="F16" s="262">
-        <v>0.5</v>
-      </c>
-      <c r="G16" s="263">
-        <v>-0.62</v>
-      </c>
-      <c r="H16" s="264">
-        <v>-0.77000000000000002</v>
-      </c>
-      <c r="I16" s="265">
-        <v>-0.070000000000000007</v>
-      </c>
-      <c r="J16" s="262">
-        <v>0.5</v>
-      </c>
-      <c r="K16" s="266">
-        <v>-1.3</v>
-      </c>
-      <c r="L16" s="267">
-        <v>-1.0600000000000001</v>
-      </c>
-      <c r="M16" s="268">
-        <v>-0.64000000000000001</v>
-      </c>
-      <c r="N16" s="269">
-        <v>-0.92000000000000004</v>
-      </c>
-      <c r="O16" s="270">
-        <v>-0.83999999999999997</v>
-      </c>
-      <c r="P16" s="271">
-        <v>-0.76000000000000001</v>
-      </c>
-      <c r="Q16" s="272">
-        <v>-0.67805012799999997</v>
-      </c>
-      <c r="R16" s="273">
-        <v>-1.409333736</v>
-      </c>
-      <c r="S16" s="274">
-        <v>-0.463666892</v>
-      </c>
-      <c r="T16" s="275">
-        <v>0.33085023699999999</v>
-      </c>
-      <c r="U16" s="276">
-        <v>-0.32966694800000002</v>
-      </c>
-      <c r="V16" s="277">
-        <v>0.38930048299999997</v>
-      </c>
-      <c r="W16" s="278">
-        <v>0.21675033299999999</v>
-      </c>
-      <c r="X16" s="279">
-        <v>-0.29347554599999998</v>
-      </c>
-      <c r="Y16" s="280">
-        <v>0.25382554499999999</v>
-      </c>
-      <c r="Z16" s="281">
-        <v>0.6166682</v>
-      </c>
-      <c r="AA16" s="282">
-        <v>0.093466933000000002</v>
-      </c>
-      <c r="AB16" s="262">
-        <v>0.50140167400000002</v>
-      </c>
-      <c r="AC16" s="283">
-        <v>0.47940184200000002</v>
+      <c r="C16" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="D16" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="E16" s="21">
+        <v>0.37875429999999999</v>
+      </c>
+      <c r="F16" s="260">
+        <v>0.69915179999999999</v>
+      </c>
+      <c r="G16" s="257">
+        <v>0.60711749999999998</v>
+      </c>
+      <c r="H16" s="261">
+        <v>0.62193120000000002</v>
+      </c>
+      <c r="I16" s="262">
+        <v>0.66691880000000003</v>
+      </c>
+      <c r="J16" s="263">
+        <v>0.72976019999999997</v>
+      </c>
+      <c r="K16" s="264">
+        <v>0.8200151</v>
+      </c>
+      <c r="L16" s="265">
+        <v>0.85024560000000005</v>
+      </c>
+      <c r="M16" s="264">
+        <v>0.81908329999999996</v>
+      </c>
+      <c r="N16" s="266">
+        <v>0.84076850000000003</v>
+      </c>
+      <c r="O16" s="267">
+        <v>0.73471509999999995</v>
+      </c>
+      <c r="P16" s="268">
+        <v>0.81532930000000003</v>
+      </c>
+      <c r="Q16" s="269">
+        <v>0.85584930000000004</v>
+      </c>
+      <c r="R16" s="270">
+        <v>0.76952310000000002</v>
+      </c>
+      <c r="S16" s="271">
+        <v>0.84147269999999996</v>
+      </c>
+      <c r="T16" s="272">
+        <v>0.83750100000000005</v>
+      </c>
+      <c r="U16" s="265">
+        <v>0.84963250000000001</v>
+      </c>
+      <c r="V16" s="273">
+        <v>0.84832779999999997</v>
+      </c>
+      <c r="W16" s="274">
+        <v>0.67176990000000003</v>
+      </c>
+      <c r="X16" s="275">
+        <v>0.73903719999999995</v>
+      </c>
+      <c r="Y16" s="276">
+        <v>0.83365630000000002</v>
+      </c>
+      <c r="Z16" s="277">
+        <v>0.86915489999999995</v>
+      </c>
+      <c r="AA16" s="278">
+        <v>0.80796939999999995</v>
+      </c>
+      <c r="AB16" s="269">
+        <v>0.85625890000000004</v>
+      </c>
+      <c r="AC16" s="279">
+        <v>0.87420600000000004</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="284" t="s">
-        <v>54</v>
-      </c>
-      <c r="B17" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="C17" s="7" t="s">
+      <c r="A17" s="280"/>
+      <c r="B17" s="33" t="s">
         <v>56</v>
       </c>
-      <c r="D17" s="8" t="s">
+      <c r="C17" s="34" t="s">
         <v>57</v>
       </c>
-      <c r="E17" s="21">
-        <v>0.37875429999999999</v>
-      </c>
-      <c r="F17" s="285">
-        <v>0.69915179999999999</v>
-      </c>
-      <c r="G17" s="286">
-        <v>0.60711749999999998</v>
-      </c>
-      <c r="H17" s="287">
-        <v>0.62193120000000002</v>
-      </c>
-      <c r="I17" s="288">
-        <v>0.66691880000000003</v>
-      </c>
-      <c r="J17" s="289">
-        <v>0.72976019999999997</v>
-      </c>
-      <c r="K17" s="290">
-        <v>0.8200151</v>
-      </c>
-      <c r="L17" s="291">
-        <v>0.85024560000000005</v>
-      </c>
-      <c r="M17" s="290">
-        <v>0.81908329999999996</v>
-      </c>
-      <c r="N17" s="292">
-        <v>0.84076850000000003</v>
-      </c>
-      <c r="O17" s="293">
-        <v>0.73471509999999995</v>
-      </c>
-      <c r="P17" s="294">
-        <v>0.81532930000000003</v>
-      </c>
-      <c r="Q17" s="295">
-        <v>0.85584930000000004</v>
-      </c>
-      <c r="R17" s="296">
-        <v>0.76952310000000002</v>
-      </c>
-      <c r="S17" s="297">
-        <v>0.84147269999999996</v>
-      </c>
-      <c r="T17" s="298">
-        <v>0.83750100000000005</v>
-      </c>
-      <c r="U17" s="291">
-        <v>0.84963250000000001</v>
-      </c>
-      <c r="V17" s="299">
-        <v>0.84832779999999997</v>
-      </c>
-      <c r="W17" s="300">
-        <v>0.67176990000000003</v>
-      </c>
-      <c r="X17" s="301">
-        <v>0.73903719999999995</v>
-      </c>
-      <c r="Y17" s="302">
-        <v>0.83365630000000002</v>
-      </c>
-      <c r="Z17" s="303">
-        <v>0.86915489999999995</v>
-      </c>
-      <c r="AA17" s="304">
-        <v>0.80796939999999995</v>
-      </c>
-      <c r="AB17" s="295">
-        <v>0.85625890000000004</v>
-      </c>
-      <c r="AC17" s="305">
-        <v>0.87420600000000004</v>
+      <c r="D17" s="35" t="s">
+        <v>58</v>
+      </c>
+      <c r="E17" s="170">
+        <v>16.949000000000002</v>
+      </c>
+      <c r="F17" s="209">
+        <v>16.765999999999998</v>
+      </c>
+      <c r="G17" s="194">
+        <v>16.800000000000001</v>
+      </c>
+      <c r="H17" s="281">
+        <v>16.661999999999999</v>
+      </c>
+      <c r="I17" s="189">
+        <v>18.210000000000001</v>
+      </c>
+      <c r="J17" s="230">
+        <v>17.227</v>
+      </c>
+      <c r="K17" s="282">
+        <v>14.737</v>
+      </c>
+      <c r="L17" s="51">
+        <v>15.715999999999999</v>
+      </c>
+      <c r="M17" s="54">
+        <v>16.186</v>
+      </c>
+      <c r="N17" s="283">
+        <v>14.233000000000001</v>
+      </c>
+      <c r="O17" s="165">
+        <v>15.949999999999999</v>
+      </c>
+      <c r="P17" s="155">
+        <v>16.233000000000001</v>
+      </c>
+      <c r="Q17" s="182">
+        <v>18.870999999999999</v>
+      </c>
+      <c r="R17" s="284">
+        <v>18.521999999999998</v>
+      </c>
+      <c r="S17" s="49">
+        <v>20.896000000000001</v>
+      </c>
+      <c r="T17" s="285">
+        <v>15.492000000000001</v>
+      </c>
+      <c r="U17" s="164">
+        <v>19.666</v>
+      </c>
+      <c r="V17" s="47">
+        <v>17.539999999999999</v>
+      </c>
+      <c r="W17" s="186">
+        <v>20.579999999999998</v>
+      </c>
+      <c r="X17" s="62">
+        <v>17.437999999999999</v>
+      </c>
+      <c r="Y17" s="231">
+        <v>17.617999999999999</v>
+      </c>
+      <c r="Z17" s="37">
+        <v>13.353</v>
+      </c>
+      <c r="AA17" s="215">
+        <v>16.988</v>
+      </c>
+      <c r="AB17" s="286">
+        <v>14.852</v>
+      </c>
+      <c r="AC17" s="287">
+        <v>16.658999999999999</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="306"/>
-      <c r="B18" s="33" t="s">
-        <v>58</v>
-      </c>
+      <c r="A18" s="280"/>
+      <c r="B18" s="33"/>
       <c r="C18" s="34" t="s">
         <v>59</v>
       </c>
       <c r="D18" s="35" t="s">
         <v>60</v>
       </c>
-      <c r="E18" s="170">
-        <v>16.949000000000002</v>
-      </c>
-      <c r="F18" s="209">
-        <v>16.765999999999998</v>
-      </c>
-      <c r="G18" s="194">
-        <v>16.800000000000001</v>
-      </c>
-      <c r="H18" s="307">
-        <v>16.661999999999999</v>
-      </c>
-      <c r="I18" s="189">
-        <v>18.210000000000001</v>
-      </c>
-      <c r="J18" s="230">
-        <v>17.227</v>
-      </c>
-      <c r="K18" s="308">
-        <v>14.737</v>
-      </c>
-      <c r="L18" s="51">
-        <v>15.715999999999999</v>
-      </c>
-      <c r="M18" s="54">
-        <v>16.186</v>
-      </c>
-      <c r="N18" s="309">
-        <v>14.233000000000001</v>
-      </c>
-      <c r="O18" s="165">
-        <v>15.949999999999999</v>
-      </c>
-      <c r="P18" s="155">
-        <v>16.233000000000001</v>
-      </c>
-      <c r="Q18" s="182">
-        <v>18.870999999999999</v>
-      </c>
-      <c r="R18" s="310">
-        <v>18.521999999999998</v>
-      </c>
-      <c r="S18" s="49">
-        <v>20.896000000000001</v>
-      </c>
-      <c r="T18" s="311">
-        <v>15.492000000000001</v>
-      </c>
-      <c r="U18" s="164">
-        <v>19.666</v>
-      </c>
-      <c r="V18" s="47">
-        <v>17.539999999999999</v>
-      </c>
-      <c r="W18" s="186">
-        <v>20.579999999999998</v>
-      </c>
-      <c r="X18" s="62">
-        <v>17.437999999999999</v>
-      </c>
-      <c r="Y18" s="231">
-        <v>17.617999999999999</v>
-      </c>
-      <c r="Z18" s="37">
-        <v>13.353</v>
-      </c>
-      <c r="AA18" s="215">
-        <v>16.988</v>
-      </c>
-      <c r="AB18" s="312">
-        <v>14.852</v>
-      </c>
-      <c r="AC18" s="313">
-        <v>16.658999999999999</v>
+      <c r="E18" s="97">
+        <v>21.634</v>
+      </c>
+      <c r="F18" s="187">
+        <v>21.588000000000001</v>
+      </c>
+      <c r="G18" s="191">
+        <v>19.774999999999999</v>
+      </c>
+      <c r="H18" s="288">
+        <v>20.419</v>
+      </c>
+      <c r="I18" s="46">
+        <v>20.684999999999999</v>
+      </c>
+      <c r="J18" s="58">
+        <v>19.196000000000002</v>
+      </c>
+      <c r="K18" s="37">
+        <v>17.768000000000001</v>
+      </c>
+      <c r="L18" s="215">
+        <v>20.045999999999999</v>
+      </c>
+      <c r="M18" s="289">
+        <v>18.158000000000001</v>
+      </c>
+      <c r="N18" s="64">
+        <v>17.965</v>
+      </c>
+      <c r="O18" s="47">
+        <v>20.408000000000001</v>
+      </c>
+      <c r="P18" s="190">
+        <v>18.963999999999999</v>
+      </c>
+      <c r="Q18" s="290">
+        <v>18.948</v>
+      </c>
+      <c r="R18" s="291">
+        <v>21.547999999999998</v>
+      </c>
+      <c r="S18" s="292">
+        <v>20.065000000000001</v>
+      </c>
+      <c r="T18" s="293">
+        <v>18.039999999999999</v>
+      </c>
+      <c r="U18" s="94">
+        <v>21.309000000000001</v>
+      </c>
+      <c r="V18" s="180">
+        <v>18.260999999999999</v>
+      </c>
+      <c r="W18" s="221">
+        <v>18.802</v>
+      </c>
+      <c r="X18" s="156">
+        <v>21.533999999999999</v>
+      </c>
+      <c r="Y18" s="182">
+        <v>21.231000000000002</v>
+      </c>
+      <c r="Z18" s="183">
+        <v>20.878</v>
+      </c>
+      <c r="AA18" s="61">
+        <v>20.553999999999998</v>
+      </c>
+      <c r="AB18" s="73">
+        <v>21.425000000000001</v>
+      </c>
+      <c r="AC18" s="294">
+        <v>22.5</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="306"/>
-      <c r="B19" s="33"/>
+      <c r="A19" s="280"/>
+      <c r="B19" s="33" t="s">
+        <v>61</v>
+      </c>
       <c r="C19" s="34" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="D19" s="35" t="s">
-        <v>62</v>
-      </c>
-      <c r="E19" s="97">
-        <v>21.634</v>
-      </c>
-      <c r="F19" s="187">
-        <v>21.588000000000001</v>
-      </c>
-      <c r="G19" s="191">
-        <v>19.774999999999999</v>
-      </c>
-      <c r="H19" s="314">
-        <v>20.419</v>
-      </c>
-      <c r="I19" s="46">
-        <v>20.684999999999999</v>
-      </c>
-      <c r="J19" s="58">
-        <v>19.196000000000002</v>
-      </c>
-      <c r="K19" s="37">
-        <v>17.768000000000001</v>
-      </c>
-      <c r="L19" s="215">
-        <v>20.045999999999999</v>
-      </c>
-      <c r="M19" s="315">
-        <v>18.158000000000001</v>
-      </c>
-      <c r="N19" s="64">
-        <v>17.965</v>
-      </c>
-      <c r="O19" s="47">
-        <v>20.408000000000001</v>
-      </c>
-      <c r="P19" s="190">
-        <v>18.963999999999999</v>
-      </c>
-      <c r="Q19" s="316">
-        <v>18.948</v>
-      </c>
-      <c r="R19" s="317">
-        <v>21.547999999999998</v>
-      </c>
-      <c r="S19" s="318">
-        <v>20.065000000000001</v>
-      </c>
-      <c r="T19" s="319">
-        <v>18.039999999999999</v>
-      </c>
-      <c r="U19" s="94">
-        <v>21.309000000000001</v>
-      </c>
-      <c r="V19" s="180">
-        <v>18.260999999999999</v>
-      </c>
-      <c r="W19" s="221">
-        <v>18.802</v>
-      </c>
-      <c r="X19" s="156">
-        <v>21.533999999999999</v>
-      </c>
-      <c r="Y19" s="182">
-        <v>21.231000000000002</v>
-      </c>
-      <c r="Z19" s="183">
-        <v>20.878</v>
-      </c>
-      <c r="AA19" s="61">
-        <v>20.553999999999998</v>
-      </c>
-      <c r="AB19" s="73">
-        <v>21.425000000000001</v>
-      </c>
-      <c r="AC19" s="320">
-        <v>22.5</v>
+        <v>60</v>
+      </c>
+      <c r="E19" s="231">
+        <v>-6.2599999999999998</v>
+      </c>
+      <c r="F19" s="37">
+        <v>-8.1899999999999995</v>
+      </c>
+      <c r="G19" s="295">
+        <v>-6.3099999999999996</v>
+      </c>
+      <c r="H19" s="228">
+        <v>-6.1399999999999997</v>
+      </c>
+      <c r="I19" s="296">
+        <v>-6.1100000000000003</v>
+      </c>
+      <c r="J19" s="43">
+        <v>-6.3499999999999996</v>
+      </c>
+      <c r="K19" s="43">
+        <v>-6.3499999999999996</v>
+      </c>
+      <c r="L19" s="57">
+        <v>-5.8200000000000003</v>
+      </c>
+      <c r="M19" s="297">
+        <v>-6.46</v>
+      </c>
+      <c r="N19" s="165">
+        <v>-7.0099999999999998</v>
+      </c>
+      <c r="O19" s="234">
+        <v>-6.2400000000000002</v>
+      </c>
+      <c r="P19" s="174">
+        <v>-6.3200000000000003</v>
+      </c>
+      <c r="Q19" s="175">
+        <v>-5.3499999999999996</v>
+      </c>
+      <c r="R19" s="49">
+        <v>-4.7699999999999996</v>
+      </c>
+      <c r="S19" s="292">
+        <v>-6.5300000000000002</v>
+      </c>
+      <c r="T19" s="177">
+        <v>-6.3799999999999999</v>
+      </c>
+      <c r="U19" s="298">
+        <v>-4.8899999999999997</v>
+      </c>
+      <c r="V19" s="227">
+        <v>-5.7999999999999998</v>
+      </c>
+      <c r="W19" s="231">
+        <v>-6.2599999999999998</v>
+      </c>
+      <c r="X19" s="299">
+        <v>-5.3099999999999996</v>
+      </c>
+      <c r="Y19" s="72">
+        <v>-4.8499999999999996</v>
+      </c>
+      <c r="Z19" s="172">
+        <v>-5.7300000000000004</v>
+      </c>
+      <c r="AA19" s="234">
+        <v>-6.25</v>
+      </c>
+      <c r="AB19" s="183">
+        <v>-5.9400000000000004</v>
+      </c>
+      <c r="AC19" s="300">
+        <v>-4.8099999999999996</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="306"/>
+      <c r="A20" s="280"/>
       <c r="B20" s="33" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C20" s="34" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="D20" s="35" t="s">
-        <v>62</v>
-      </c>
-      <c r="E20" s="231">
-        <v>-6.2599999999999998</v>
-      </c>
-      <c r="F20" s="37">
-        <v>-8.1899999999999995</v>
-      </c>
-      <c r="G20" s="321">
-        <v>-6.3099999999999996</v>
-      </c>
-      <c r="H20" s="228">
-        <v>-6.1399999999999997</v>
-      </c>
-      <c r="I20" s="322">
-        <v>-6.1100000000000003</v>
-      </c>
-      <c r="J20" s="43">
-        <v>-6.3499999999999996</v>
-      </c>
-      <c r="K20" s="43">
-        <v>-6.3499999999999996</v>
-      </c>
-      <c r="L20" s="57">
-        <v>-5.8200000000000003</v>
-      </c>
-      <c r="M20" s="323">
-        <v>-6.46</v>
-      </c>
-      <c r="N20" s="165">
-        <v>-7.0099999999999998</v>
-      </c>
-      <c r="O20" s="234">
-        <v>-6.2400000000000002</v>
-      </c>
-      <c r="P20" s="174">
-        <v>-6.3200000000000003</v>
-      </c>
-      <c r="Q20" s="175">
-        <v>-5.3499999999999996</v>
-      </c>
-      <c r="R20" s="49">
-        <v>-4.7699999999999996</v>
-      </c>
-      <c r="S20" s="318">
-        <v>-6.5300000000000002</v>
-      </c>
-      <c r="T20" s="177">
-        <v>-6.3799999999999999</v>
-      </c>
-      <c r="U20" s="324">
-        <v>-4.8899999999999997</v>
-      </c>
-      <c r="V20" s="227">
-        <v>-5.7999999999999998</v>
-      </c>
-      <c r="W20" s="231">
-        <v>-6.2599999999999998</v>
-      </c>
-      <c r="X20" s="325">
-        <v>-5.3099999999999996</v>
-      </c>
-      <c r="Y20" s="72">
-        <v>-4.8499999999999996</v>
-      </c>
-      <c r="Z20" s="172">
-        <v>-5.7300000000000004</v>
-      </c>
-      <c r="AA20" s="234">
-        <v>-6.25</v>
-      </c>
-      <c r="AB20" s="183">
-        <v>-5.9400000000000004</v>
-      </c>
-      <c r="AC20" s="326">
-        <v>-4.8099999999999996</v>
+        <v>60</v>
+      </c>
+      <c r="E20" s="220">
+        <v>2.4500000000000002</v>
+      </c>
+      <c r="F20" s="63">
+        <v>2.5800000000000001</v>
+      </c>
+      <c r="G20" s="194">
+        <v>2.5</v>
+      </c>
+      <c r="H20" s="301">
+        <v>2.54</v>
+      </c>
+      <c r="I20" s="302">
+        <v>2.5299999999999998</v>
+      </c>
+      <c r="J20" s="302">
+        <v>2.5299999999999998</v>
+      </c>
+      <c r="K20" s="303">
+        <v>2.4399999999999999</v>
+      </c>
+      <c r="L20" s="153">
+        <v>2.52</v>
+      </c>
+      <c r="M20" s="220">
+        <v>2.4500000000000002</v>
+      </c>
+      <c r="N20" s="88">
+        <v>2.46</v>
+      </c>
+      <c r="O20" s="303">
+        <v>2.4399999999999999</v>
+      </c>
+      <c r="P20" s="98">
+        <v>2.4700000000000002</v>
+      </c>
+      <c r="Q20" s="301">
+        <v>2.54</v>
+      </c>
+      <c r="R20" s="207">
+        <v>2.5099999999999998</v>
+      </c>
+      <c r="S20" s="304">
+        <v>2.3999999999999999</v>
+      </c>
+      <c r="T20" s="37">
+        <v>2.6000000000000001</v>
+      </c>
+      <c r="U20" s="49">
+        <v>2.3799999999999999</v>
+      </c>
+      <c r="V20" s="305">
+        <v>2.4900000000000002</v>
+      </c>
+      <c r="W20" s="220">
+        <v>2.4500000000000002</v>
+      </c>
+      <c r="X20" s="73">
+        <v>2.4300000000000002</v>
+      </c>
+      <c r="Y20" s="73">
+        <v>2.4300000000000002</v>
+      </c>
+      <c r="Z20" s="301">
+        <v>2.54</v>
+      </c>
+      <c r="AA20" s="73">
+        <v>2.4300000000000002</v>
+      </c>
+      <c r="AB20" s="194">
+        <v>2.5</v>
+      </c>
+      <c r="AC20" s="306">
+        <v>2.5299999999999998</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="306"/>
+      <c r="A21" s="280"/>
       <c r="B21" s="33" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C21" s="34" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="D21" s="35" t="s">
-        <v>62</v>
-      </c>
-      <c r="E21" s="220">
-        <v>2.4500000000000002</v>
-      </c>
-      <c r="F21" s="63">
-        <v>2.5800000000000001</v>
-      </c>
-      <c r="G21" s="194">
-        <v>2.5</v>
-      </c>
-      <c r="H21" s="327">
-        <v>2.54</v>
-      </c>
-      <c r="I21" s="328">
-        <v>2.5299999999999998</v>
-      </c>
-      <c r="J21" s="328">
-        <v>2.5299999999999998</v>
-      </c>
-      <c r="K21" s="329">
-        <v>2.4399999999999999</v>
-      </c>
-      <c r="L21" s="153">
-        <v>2.52</v>
-      </c>
-      <c r="M21" s="220">
-        <v>2.4500000000000002</v>
+        <v>60</v>
+      </c>
+      <c r="E21" s="307">
+        <v>12.068796769522001</v>
+      </c>
+      <c r="F21" s="308">
+        <v>12.178733965341999</v>
+      </c>
+      <c r="G21" s="69">
+        <v>11.303890911152999</v>
+      </c>
+      <c r="H21" s="222">
+        <v>11.865747928207</v>
+      </c>
+      <c r="I21" s="282">
+        <v>11.939961005403999</v>
+      </c>
+      <c r="J21" s="37">
+        <v>12.229382074528999</v>
+      </c>
+      <c r="K21" s="309">
+        <v>10.985252293644001</v>
+      </c>
+      <c r="L21" s="310">
+        <v>11.612237895765</v>
+      </c>
+      <c r="M21" s="149">
+        <v>11.407011330015999</v>
       </c>
       <c r="N21" s="88">
-        <v>2.46</v>
-      </c>
-      <c r="O21" s="329">
-        <v>2.4399999999999999</v>
-      </c>
-      <c r="P21" s="98">
-        <v>2.4700000000000002</v>
-      </c>
-      <c r="Q21" s="327">
-        <v>2.54</v>
-      </c>
-      <c r="R21" s="207">
-        <v>2.5099999999999998</v>
-      </c>
-      <c r="S21" s="330">
-        <v>2.3999999999999999</v>
-      </c>
-      <c r="T21" s="37">
-        <v>2.6000000000000001</v>
-      </c>
-      <c r="U21" s="49">
-        <v>2.3799999999999999</v>
-      </c>
-      <c r="V21" s="331">
-        <v>2.4900000000000002</v>
-      </c>
-      <c r="W21" s="220">
-        <v>2.4500000000000002</v>
-      </c>
-      <c r="X21" s="73">
-        <v>2.4300000000000002</v>
-      </c>
-      <c r="Y21" s="73">
-        <v>2.4300000000000002</v>
-      </c>
-      <c r="Z21" s="327">
-        <v>2.54</v>
-      </c>
-      <c r="AA21" s="73">
-        <v>2.4300000000000002</v>
-      </c>
-      <c r="AB21" s="194">
-        <v>2.5</v>
-      </c>
-      <c r="AC21" s="332">
-        <v>2.5299999999999998</v>
+        <v>11.216207993360999</v>
+      </c>
+      <c r="O21" s="49">
+        <v>10.636929263246</v>
+      </c>
+      <c r="P21" s="311">
+        <v>11.154825855464001</v>
+      </c>
+      <c r="Q21" s="312">
+        <v>11.701118087351</v>
+      </c>
+      <c r="R21" s="232">
+        <v>11.686571095545</v>
+      </c>
+      <c r="S21" s="156">
+        <v>10.961510535186999</v>
+      </c>
+      <c r="T21" s="82">
+        <v>11.737438509357</v>
+      </c>
+      <c r="U21" s="183">
+        <v>11.182010209035001</v>
+      </c>
+      <c r="V21" s="157">
+        <v>11.221832898278</v>
+      </c>
+      <c r="W21" s="69">
+        <v>11.308359184045001</v>
+      </c>
+      <c r="X21" s="152">
+        <v>10.994139727594</v>
+      </c>
+      <c r="Y21" s="313">
+        <v>10.768269634001999</v>
+      </c>
+      <c r="Z21" s="297">
+        <v>11.422651349911</v>
+      </c>
+      <c r="AA21" s="77">
+        <v>10.988108896327001</v>
+      </c>
+      <c r="AB21" s="80">
+        <v>11.771403359833</v>
+      </c>
+      <c r="AC21" s="314">
+        <v>11.596738687666999</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="306"/>
-      <c r="B22" s="33" t="s">
+      <c r="A22" s="280"/>
+      <c r="B22" s="33"/>
+      <c r="C22" s="34" t="s">
+        <v>64</v>
+      </c>
+      <c r="D22" s="35" t="s">
         <v>65</v>
       </c>
-      <c r="C22" s="34" t="s">
-        <v>61</v>
-      </c>
-      <c r="D22" s="35" t="s">
-        <v>62</v>
-      </c>
-      <c r="E22" s="333">
-        <v>12.1</v>
-      </c>
-      <c r="F22" s="37">
-        <v>12.199999999999999</v>
-      </c>
-      <c r="G22" s="314">
-        <v>11.300000000000001</v>
-      </c>
-      <c r="H22" s="185">
-        <v>11.9</v>
-      </c>
-      <c r="I22" s="185">
-        <v>11.9</v>
-      </c>
-      <c r="J22" s="37">
-        <v>12.199999999999999</v>
-      </c>
-      <c r="K22" s="94">
-        <v>11</v>
-      </c>
-      <c r="L22" s="91">
-        <v>11.6</v>
-      </c>
-      <c r="M22" s="331">
-        <v>11.4</v>
-      </c>
-      <c r="N22" s="211">
-        <v>11.199999999999999</v>
-      </c>
-      <c r="O22" s="49">
-        <v>10.6</v>
-      </c>
-      <c r="P22" s="211">
-        <v>11.199999999999999</v>
-      </c>
-      <c r="Q22" s="51">
-        <v>11.699999999999999</v>
-      </c>
-      <c r="R22" s="51">
-        <v>11.699999999999999</v>
-      </c>
-      <c r="S22" s="94">
-        <v>11</v>
-      </c>
-      <c r="T22" s="51">
-        <v>11.699999999999999</v>
-      </c>
-      <c r="U22" s="211">
-        <v>11.199999999999999</v>
-      </c>
-      <c r="V22" s="211">
-        <v>11.199999999999999</v>
-      </c>
-      <c r="W22" s="314">
-        <v>11.300000000000001</v>
-      </c>
-      <c r="X22" s="94">
-        <v>11</v>
-      </c>
-      <c r="Y22" s="334">
-        <v>10.800000000000001</v>
-      </c>
-      <c r="Z22" s="331">
-        <v>11.4</v>
-      </c>
-      <c r="AA22" s="94">
-        <v>11</v>
-      </c>
-      <c r="AB22" s="316">
-        <v>11.800000000000001</v>
-      </c>
-      <c r="AC22" s="335">
-        <v>11.6</v>
+      <c r="E22" s="40">
+        <v>0.56222222222222207</v>
+      </c>
+      <c r="F22" s="290">
+        <v>0.2722222222222222</v>
+      </c>
+      <c r="G22" s="208">
+        <v>-1.8011111111111111</v>
+      </c>
+      <c r="H22" s="192">
+        <v>-1.612222222222222</v>
+      </c>
+      <c r="I22" s="299">
+        <v>-1.5011111111111111</v>
+      </c>
+      <c r="J22" s="49">
+        <v>-1.975555555555556</v>
+      </c>
+      <c r="K22" s="311">
+        <v>-1.004444444444444</v>
+      </c>
+      <c r="L22" s="315">
+        <v>-1.4199999999999999</v>
+      </c>
+      <c r="M22" s="225">
+        <v>-0.5788888888888889</v>
+      </c>
+      <c r="N22" s="194">
+        <v>-0.3477777777777778</v>
+      </c>
+      <c r="O22" s="216">
+        <v>-0.84444444444444455</v>
+      </c>
+      <c r="P22" s="225">
+        <v>-0.57666666666666677</v>
+      </c>
+      <c r="Q22" s="225">
+        <v>-0.57444444444444442</v>
+      </c>
+      <c r="R22" s="89">
+        <v>-0.89111111111111108</v>
+      </c>
+      <c r="S22" s="316">
+        <v>0.30777777777777782</v>
+      </c>
+      <c r="T22" s="37">
+        <v>1.0177777777777779</v>
+      </c>
+      <c r="U22" s="284">
+        <v>-1.0377777777777779</v>
+      </c>
+      <c r="V22" s="317">
+        <v>-0.31</v>
+      </c>
+      <c r="W22" s="194">
+        <v>-0.34444444444444439</v>
+      </c>
+      <c r="X22" s="309">
+        <v>-1.3277777777777779</v>
+      </c>
+      <c r="Y22" s="168">
+        <v>-0.085555555555555496</v>
+      </c>
+      <c r="Z22" s="70">
+        <v>-0.45555555555555549</v>
+      </c>
+      <c r="AA22" s="89">
+        <v>-0.89111111111111108</v>
+      </c>
+      <c r="AB22" s="84">
+        <v>-0.32222222222222219</v>
+      </c>
+      <c r="AC22" s="318">
+        <v>-1.0811111111111109</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="306"/>
+      <c r="A23" s="280"/>
       <c r="B23" s="33"/>
       <c r="C23" s="34" t="s">
         <v>66</v>
@@ -5296,84 +5236,76 @@
       <c r="D23" s="35" t="s">
         <v>67</v>
       </c>
-      <c r="E23" s="40">
-        <v>0.56222222222222207</v>
-      </c>
-      <c r="F23" s="316">
-        <v>0.2722222222222222</v>
-      </c>
-      <c r="G23" s="208">
-        <v>-1.8011111111111111</v>
-      </c>
-      <c r="H23" s="192">
-        <v>-1.612222222222222</v>
-      </c>
-      <c r="I23" s="325">
-        <v>-1.5011111111111111</v>
-      </c>
-      <c r="J23" s="49">
-        <v>-1.975555555555556</v>
-      </c>
-      <c r="K23" s="336">
-        <v>-1.004444444444444</v>
-      </c>
-      <c r="L23" s="337">
-        <v>-1.4199999999999999</v>
-      </c>
-      <c r="M23" s="225">
-        <v>-0.5788888888888889</v>
-      </c>
-      <c r="N23" s="194">
-        <v>-0.3477777777777778</v>
-      </c>
-      <c r="O23" s="216">
-        <v>-0.84444444444444455</v>
-      </c>
-      <c r="P23" s="225">
-        <v>-0.57666666666666677</v>
-      </c>
-      <c r="Q23" s="225">
-        <v>-0.57444444444444442</v>
-      </c>
-      <c r="R23" s="89">
-        <v>-0.89111111111111108</v>
-      </c>
-      <c r="S23" s="338">
-        <v>0.30777777777777782</v>
-      </c>
-      <c r="T23" s="37">
-        <v>1.0177777777777779</v>
-      </c>
-      <c r="U23" s="310">
-        <v>-1.0377777777777779</v>
-      </c>
-      <c r="V23" s="339">
-        <v>-0.31</v>
-      </c>
-      <c r="W23" s="194">
-        <v>-0.34444444444444439</v>
-      </c>
-      <c r="X23" s="340">
-        <v>-1.3277777777777779</v>
-      </c>
-      <c r="Y23" s="168">
-        <v>-0.085555555555555496</v>
-      </c>
-      <c r="Z23" s="70">
-        <v>-0.45555555555555549</v>
-      </c>
-      <c r="AA23" s="89">
-        <v>-0.89111111111111108</v>
-      </c>
-      <c r="AB23" s="84">
-        <v>-0.32222222222222219</v>
-      </c>
-      <c r="AC23" s="341">
-        <v>-1.0811111111111109</v>
+      <c r="E23" s="319"/>
+      <c r="F23" s="319"/>
+      <c r="G23" s="319"/>
+      <c r="H23" s="319"/>
+      <c r="I23" s="57">
+        <v>10.539999999999999</v>
+      </c>
+      <c r="J23" s="217">
+        <v>11.73</v>
+      </c>
+      <c r="K23" s="89">
+        <v>10.890000000000001</v>
+      </c>
+      <c r="L23" s="162">
+        <v>11.970000000000001</v>
+      </c>
+      <c r="M23" s="51">
+        <v>13.02</v>
+      </c>
+      <c r="N23" s="149">
+        <v>11.69</v>
+      </c>
+      <c r="O23" s="162">
+        <v>11.960000000000001</v>
+      </c>
+      <c r="P23" s="320">
+        <v>12.35</v>
+      </c>
+      <c r="Q23" s="37">
+        <v>15.07</v>
+      </c>
+      <c r="R23" s="70">
+        <v>11.84</v>
+      </c>
+      <c r="S23" s="321">
+        <v>9.1400000000000006</v>
+      </c>
+      <c r="T23" s="322">
+        <v>12.43</v>
+      </c>
+      <c r="U23" s="38">
+        <v>10.56</v>
+      </c>
+      <c r="V23" s="197">
+        <v>10.4</v>
+      </c>
+      <c r="W23" s="228">
+        <v>11.15</v>
+      </c>
+      <c r="X23" s="49">
+        <v>8.5199999999999996</v>
+      </c>
+      <c r="Y23" s="323">
+        <v>8.9199999999999999</v>
+      </c>
+      <c r="Z23" s="284">
+        <v>10.58</v>
+      </c>
+      <c r="AA23" s="173">
+        <v>9.5299999999999994</v>
+      </c>
+      <c r="AB23" s="205">
+        <v>10.25</v>
+      </c>
+      <c r="AC23" s="84">
+        <v>12.130000000000001</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="306"/>
+      <c r="A24" s="280"/>
       <c r="B24" s="33" t="s">
         <v>68</v>
       </c>
@@ -5383,19 +5315,19 @@
       <c r="D24" s="35" t="s">
         <v>70</v>
       </c>
-      <c r="E24" s="342">
+      <c r="E24" s="324">
         <v>99.480000000000004</v>
       </c>
-      <c r="F24" s="343">
+      <c r="F24" s="325">
         <v>96.760000000000005</v>
       </c>
       <c r="G24" s="63">
         <v>95.810000000000002</v>
       </c>
-      <c r="H24" s="343">
+      <c r="H24" s="325">
         <v>96.700000000000003</v>
       </c>
-      <c r="I24" s="344">
+      <c r="I24" s="307">
         <v>95.5</v>
       </c>
       <c r="J24" s="37">
@@ -5404,7 +5336,7 @@
       <c r="K24" s="63">
         <v>95.780000000000001</v>
       </c>
-      <c r="L24" s="345">
+      <c r="L24" s="326">
         <v>96.900000000000006</v>
       </c>
       <c r="M24" s="179">
@@ -5419,7 +5351,7 @@
       <c r="P24" s="40">
         <v>93.200000000000003</v>
       </c>
-      <c r="Q24" s="346">
+      <c r="Q24" s="327">
         <v>95.670000000000002</v>
       </c>
       <c r="R24" s="49">
@@ -5431,13 +5363,13 @@
       <c r="T24" s="204">
         <v>95</v>
       </c>
-      <c r="U24" s="347">
+      <c r="U24" s="312">
         <v>84.980000000000004</v>
       </c>
       <c r="V24" s="82">
         <v>85.840000000000003</v>
       </c>
-      <c r="W24" s="348">
+      <c r="W24" s="328">
         <v>90.379999999999995</v>
       </c>
       <c r="X24" s="225">
@@ -5446,15 +5378,15 @@
       <c r="Y24" s="230">
         <v>76.640000000000001</v>
       </c>
-      <c r="Z24" s="349">
+      <c r="Z24" s="329">
         <v>91.890000000000001</v>
       </c>
-      <c r="AA24" s="350"/>
-      <c r="AB24" s="350"/>
-      <c r="AC24" s="350"/>
+      <c r="AA24" s="319"/>
+      <c r="AB24" s="319"/>
+      <c r="AC24" s="319"/>
     </row>
     <row r="25">
-      <c r="A25" s="306"/>
+      <c r="A25" s="280"/>
       <c r="B25" s="33" t="s">
         <v>71</v>
       </c>
@@ -5470,7 +5402,7 @@
       <c r="F25" s="96">
         <v>92.775000000000006</v>
       </c>
-      <c r="G25" s="351">
+      <c r="G25" s="330">
         <v>95.951400000000007</v>
       </c>
       <c r="H25" s="195">
@@ -5497,16 +5429,16 @@
       <c r="O25" s="162">
         <v>82.961500000000001</v>
       </c>
-      <c r="P25" s="352">
+      <c r="P25" s="331">
         <v>87.5</v>
       </c>
       <c r="Q25" s="82">
         <v>88.357600000000005</v>
       </c>
-      <c r="R25" s="353">
+      <c r="R25" s="332">
         <v>67.878799999999998</v>
       </c>
-      <c r="S25" s="354">
+      <c r="S25" s="333">
         <v>74.793400000000005</v>
       </c>
       <c r="T25" s="223">
@@ -5515,37 +5447,37 @@
       <c r="U25" s="165">
         <v>87.195099999999996</v>
       </c>
-      <c r="V25" s="355">
+      <c r="V25" s="334">
         <v>97.012299999999996</v>
       </c>
       <c r="W25" s="37">
         <v>98.517499999999998</v>
       </c>
-      <c r="X25" s="319">
+      <c r="X25" s="293">
         <v>96.6173</v>
       </c>
-      <c r="Y25" s="356">
+      <c r="Y25" s="335">
         <v>93.207499999999996</v>
       </c>
       <c r="Z25" s="76">
         <v>90.518500000000003</v>
       </c>
-      <c r="AA25" s="350"/>
-      <c r="AB25" s="350"/>
-      <c r="AC25" s="350"/>
+      <c r="AA25" s="319"/>
+      <c r="AB25" s="319"/>
+      <c r="AC25" s="319"/>
     </row>
     <row r="26">
-      <c r="A26" s="306"/>
+      <c r="A26" s="280"/>
       <c r="B26" s="33" t="s">
         <v>74</v>
       </c>
       <c r="C26" s="34" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D26" s="35" t="s">
         <v>75</v>
       </c>
-      <c r="E26" s="357">
+      <c r="E26" s="336">
         <v>51.259999999999998</v>
       </c>
       <c r="F26" s="85">
@@ -5560,25 +5492,25 @@
       <c r="I26" s="69">
         <v>64.569999999999993</v>
       </c>
-      <c r="J26" s="311">
+      <c r="J26" s="285">
         <v>79.310000000000002</v>
       </c>
       <c r="K26" s="153">
         <v>75.329999999999998</v>
       </c>
-      <c r="L26" s="340">
+      <c r="L26" s="309">
         <v>54.549999999999997</v>
       </c>
       <c r="M26" s="165">
         <v>76.189999999999998</v>
       </c>
-      <c r="N26" s="358">
+      <c r="N26" s="337">
         <v>91.930000000000007</v>
       </c>
       <c r="O26" s="167">
         <v>65.939999999999998</v>
       </c>
-      <c r="P26" s="359">
+      <c r="P26" s="338">
         <v>92.120000000000005</v>
       </c>
       <c r="Q26" s="215">
@@ -5587,10 +5519,10 @@
       <c r="R26" s="37">
         <v>93.359999999999999</v>
       </c>
-      <c r="S26" s="351">
+      <c r="S26" s="330">
         <v>89.459999999999994</v>
       </c>
-      <c r="T26" s="312">
+      <c r="T26" s="286">
         <v>83.579999999999998</v>
       </c>
       <c r="U26" s="150">
@@ -5599,7 +5531,7 @@
       <c r="V26" s="232">
         <v>76.439999999999998</v>
       </c>
-      <c r="W26" s="360">
+      <c r="W26" s="339">
         <v>89.549999999999997</v>
       </c>
       <c r="X26" s="40">
@@ -5617,12 +5549,12 @@
       <c r="AB26" s="41">
         <v>86.719999999999999</v>
       </c>
-      <c r="AC26" s="361">
+      <c r="AC26" s="340">
         <v>71.400000000000006</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="306"/>
+      <c r="A27" s="280"/>
       <c r="B27" s="33" t="s">
         <v>76</v>
       </c>
@@ -5632,11 +5564,11 @@
       <c r="D27" s="35" t="s">
         <v>78</v>
       </c>
-      <c r="E27" s="350"/>
+      <c r="E27" s="319"/>
       <c r="F27" s="37">
         <v>68.040000000000006</v>
       </c>
-      <c r="G27" s="362">
+      <c r="G27" s="341">
         <v>52.43</v>
       </c>
       <c r="H27" s="54">
@@ -5648,19 +5580,19 @@
       <c r="J27" s="225">
         <v>47.020000000000003</v>
       </c>
-      <c r="K27" s="363">
+      <c r="K27" s="342">
         <v>40.149999999999999</v>
       </c>
-      <c r="L27" s="357">
+      <c r="L27" s="336">
         <v>34.659999999999997</v>
       </c>
       <c r="M27" s="175">
         <v>35.469999999999999</v>
       </c>
-      <c r="N27" s="364">
+      <c r="N27" s="343">
         <v>54.350000000000001</v>
       </c>
-      <c r="O27" s="314">
+      <c r="O27" s="288">
         <v>45.979999999999997</v>
       </c>
       <c r="P27" s="167">
@@ -5693,21 +5625,21 @@
       <c r="Y27" s="156">
         <v>36.75</v>
       </c>
-      <c r="Z27" s="365">
+      <c r="Z27" s="344">
         <v>30.48</v>
       </c>
       <c r="AA27" s="49">
         <v>28.739999999999998</v>
       </c>
-      <c r="AB27" s="317">
+      <c r="AB27" s="291">
         <v>36.579999999999998</v>
       </c>
-      <c r="AC27" s="366">
+      <c r="AC27" s="345">
         <v>44.670000000000002</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="306"/>
+      <c r="A28" s="280"/>
       <c r="B28" s="33" t="s">
         <v>79</v>
       </c>
@@ -5720,10 +5652,10 @@
       <c r="E28" s="49">
         <v>0.63</v>
       </c>
-      <c r="F28" s="324">
+      <c r="F28" s="298">
         <v>0.68999999999999995</v>
       </c>
-      <c r="G28" s="365">
+      <c r="G28" s="344">
         <v>0.70999999999999996</v>
       </c>
       <c r="H28" s="87">
@@ -5735,7 +5667,7 @@
       <c r="J28" s="37">
         <v>2.3500000000000001</v>
       </c>
-      <c r="K28" s="357">
+      <c r="K28" s="336">
         <v>0.89000000000000001</v>
       </c>
       <c r="L28" s="188">
@@ -5744,7 +5676,7 @@
       <c r="M28" s="188">
         <v>1.04</v>
       </c>
-      <c r="N28" s="367">
+      <c r="N28" s="346">
         <v>1.3100000000000001</v>
       </c>
       <c r="O28" s="210">
@@ -5765,7 +5697,7 @@
       <c r="T28" s="201">
         <v>1.99</v>
       </c>
-      <c r="U28" s="368">
+      <c r="U28" s="347">
         <v>0.85999999999999999</v>
       </c>
       <c r="V28" s="175">
@@ -5774,7 +5706,7 @@
       <c r="W28" s="151">
         <v>0.96999999999999997</v>
       </c>
-      <c r="X28" s="369">
+      <c r="X28" s="348">
         <v>1.0700000000000001</v>
       </c>
       <c r="Y28" s="158">
@@ -5789,12 +5721,12 @@
       <c r="AB28" s="176">
         <v>0.65000000000000002</v>
       </c>
-      <c r="AC28" s="370">
+      <c r="AC28" s="349">
         <v>1.4399999999999999</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="306"/>
+      <c r="A29" s="280"/>
       <c r="B29" s="33" t="s">
         <v>82</v>
       </c>
@@ -5804,7 +5736,7 @@
       <c r="D29" s="35" t="s">
         <v>84</v>
       </c>
-      <c r="E29" s="350"/>
+      <c r="E29" s="319"/>
       <c r="F29" s="74">
         <v>43.100000000000001</v>
       </c>
@@ -5817,49 +5749,49 @@
       <c r="I29" s="74">
         <v>43</v>
       </c>
-      <c r="J29" s="309">
+      <c r="J29" s="283">
         <v>46.200000000000003</v>
       </c>
-      <c r="K29" s="371">
+      <c r="K29" s="350">
         <v>37.299999999999997</v>
       </c>
-      <c r="L29" s="315">
+      <c r="L29" s="289">
         <v>47.399999999999999</v>
       </c>
-      <c r="M29" s="372">
+      <c r="M29" s="351">
         <v>44</v>
       </c>
-      <c r="N29" s="348">
+      <c r="N29" s="328">
         <v>42.100000000000001</v>
       </c>
-      <c r="O29" s="347">
+      <c r="O29" s="312">
         <v>37.200000000000003</v>
       </c>
-      <c r="P29" s="346">
+      <c r="P29" s="327">
         <v>47</v>
       </c>
-      <c r="Q29" s="373">
+      <c r="Q29" s="352">
         <v>44.299999999999997</v>
       </c>
-      <c r="R29" s="337">
+      <c r="R29" s="315">
         <v>16.800000000000001</v>
       </c>
       <c r="S29" s="61">
         <v>26.399999999999999</v>
       </c>
-      <c r="T29" s="309">
+      <c r="T29" s="283">
         <v>46.100000000000001</v>
       </c>
       <c r="U29" s="49">
         <v>9.0999999999999996</v>
       </c>
-      <c r="V29" s="311">
+      <c r="V29" s="285">
         <v>39.100000000000001</v>
       </c>
       <c r="W29" s="37">
         <v>51</v>
       </c>
-      <c r="X29" s="369">
+      <c r="X29" s="348">
         <v>19.899999999999999</v>
       </c>
       <c r="Y29" s="162">
@@ -5871,7 +5803,7 @@
       <c r="AA29" s="36">
         <v>40.299999999999997</v>
       </c>
-      <c r="AB29" s="374">
+      <c r="AB29" s="353">
         <v>37</v>
       </c>
       <c r="AC29" s="81">
@@ -5879,7 +5811,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="375"/>
+      <c r="A30" s="354"/>
       <c r="B30" s="102" t="s">
         <v>85</v>
       </c>
@@ -5887,89 +5819,89 @@
         <v>72</v>
       </c>
       <c r="D30" s="104" t="s">
-        <v>60</v>
-      </c>
-      <c r="E30" s="376">
-        <v>4.1044598959631937</v>
-      </c>
-      <c r="F30" s="377">
-        <v>4.8099868206094172</v>
-      </c>
-      <c r="G30" s="378">
-        <v>3.8934516198427112</v>
-      </c>
-      <c r="H30" s="379">
-        <v>3.6918749630937349</v>
+        <v>58</v>
+      </c>
+      <c r="E30" s="355">
+        <v>4.1044891960232679</v>
+      </c>
+      <c r="F30" s="356">
+        <v>4.8099681002260928</v>
+      </c>
+      <c r="G30" s="357">
+        <v>3.8934625776266638</v>
+      </c>
+      <c r="H30" s="358">
+        <v>3.6918204384354079</v>
       </c>
       <c r="I30" s="112">
-        <v>3.7059823620135979</v>
-      </c>
-      <c r="J30" s="380">
-        <v>4.5771821494479221</v>
-      </c>
-      <c r="K30" s="381">
-        <v>4.0894995105589009</v>
-      </c>
-      <c r="L30" s="382">
-        <v>4.2439133325442473</v>
-      </c>
-      <c r="M30" s="383">
-        <v>4.4612998155683892</v>
-      </c>
-      <c r="N30" s="384">
-        <v>4.3312595176202286</v>
-      </c>
-      <c r="O30" s="385">
-        <v>4.2846894017849246</v>
-      </c>
-      <c r="P30" s="385">
-        <v>4.2784700465155812</v>
-      </c>
-      <c r="Q30" s="386">
-        <v>4.0338865931849863</v>
+        <v>3.7058688513148308</v>
+      </c>
+      <c r="J30" s="359">
+        <v>4.5771934115764319</v>
+      </c>
+      <c r="K30" s="360">
+        <v>4.0894330204316844</v>
+      </c>
+      <c r="L30" s="361">
+        <v>4.2439805421517907</v>
+      </c>
+      <c r="M30" s="362">
+        <v>4.4613013591898536</v>
+      </c>
+      <c r="N30" s="363">
+        <v>4.331303322653751</v>
+      </c>
+      <c r="O30" s="364">
+        <v>4.2846926364769651</v>
+      </c>
+      <c r="P30" s="364">
+        <v>4.2784107868148826</v>
+      </c>
+      <c r="Q30" s="365">
+        <v>4.0338630183627151</v>
       </c>
       <c r="R30" s="121">
-        <v>2.4915511925066691</v>
-      </c>
-      <c r="S30" s="244">
-        <v>3.7201358437644898</v>
-      </c>
-      <c r="T30" s="237">
-        <v>4.6111522576656387</v>
-      </c>
-      <c r="U30" s="387">
-        <v>3.435276695315018</v>
-      </c>
-      <c r="V30" s="388">
-        <v>4.3485991085613636</v>
+        <v>2.4916448165081602</v>
+      </c>
+      <c r="S30" s="366">
+        <v>3.72009251423099</v>
+      </c>
+      <c r="T30" s="367">
+        <v>4.6111281821195629</v>
+      </c>
+      <c r="U30" s="368">
+        <v>3.435425128950746</v>
+      </c>
+      <c r="V30" s="369">
+        <v>4.3486469131189516</v>
       </c>
       <c r="W30" s="109">
-        <v>4.9825786963137304</v>
-      </c>
-      <c r="X30" s="389">
-        <v>3.5213479827926171</v>
-      </c>
-      <c r="Y30" s="390">
-        <v>4.2654928184179299</v>
+        <v>4.9826090593124892</v>
+      </c>
+      <c r="X30" s="370">
+        <v>3.5212903821508759</v>
+      </c>
+      <c r="Y30" s="371">
+        <v>4.2654788143210247</v>
       </c>
       <c r="Z30" s="120">
-        <v>5.7515562494610419</v>
-      </c>
-      <c r="AA30" s="350"/>
-      <c r="AB30" s="350"/>
-      <c r="AC30" s="350"/>
+        <v>5.7515484033096307</v>
+      </c>
+      <c r="AA30" s="319"/>
+      <c r="AB30" s="319"/>
+      <c r="AC30" s="319"/>
     </row>
     <row r="31" ht="14.25">
-      <c r="B31" s="391"/>
+      <c r="B31" s="372"/>
     </row>
   </sheetData>
   <mergeCells count="6">
-    <mergeCell ref="A2:A16"/>
+    <mergeCell ref="A2:A15"/>
     <mergeCell ref="B2:B6"/>
-    <mergeCell ref="B7:B15"/>
-    <mergeCell ref="A17:A30"/>
-    <mergeCell ref="B18:B19"/>
-    <mergeCell ref="B22:B23"/>
+    <mergeCell ref="B7:B14"/>
+    <mergeCell ref="A16:A30"/>
+    <mergeCell ref="B17:B18"/>
+    <mergeCell ref="B21:B23"/>
   </mergeCells>
   <printOptions headings="0" gridLines="0"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
